--- a/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
+++ b/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adisa.bylygbashi\Documents\SPL_3BHWII\CandyMachine_Watermelon\Stuecklisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292BC828-7F29-46CD-8F42-BE8FB002B2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E5A73D-E833-4122-AD06-0EF846BD5941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
   </bookViews>
   <sheets>
     <sheet name="RahmenkonstruktionOhneTuer" sheetId="1" r:id="rId1"/>
     <sheet name="VerkleidungOhneTuer" sheetId="2" r:id="rId2"/>
     <sheet name="Tuer" sheetId="3" r:id="rId3"/>
-    <sheet name="Gesamtsumme" sheetId="4" r:id="rId4"/>
+    <sheet name="Zusatzteile" sheetId="5" r:id="rId4"/>
+    <sheet name="Gesamtsumme" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="72">
   <si>
     <t>Stückliste Rahmen ohne Tür</t>
   </si>
@@ -128,25 +129,6 @@
     <t>Seitenwand links (Stahlblech 0,55 mm) 600x400</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="Amazon Ember"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>‎SPL1203000750400600</t>
-    </r>
-  </si>
-  <si>
     <t>Amazon</t>
   </si>
   <si>
@@ -174,9 +156,6 @@
     <t>Weiterverwendung  - M3 Schrauben Set von RahmenkonstruktionOhneTuer</t>
   </si>
   <si>
-    <t>~32,86</t>
-  </si>
-  <si>
     <t>Stückliste Tuer</t>
   </si>
   <si>
@@ -192,12 +171,6 @@
     <t>Tuerblech-Grundplatte</t>
   </si>
   <si>
-    <t>SPLVERZ000750400600</t>
-  </si>
-  <si>
-    <t>ca. 4,74</t>
-  </si>
-  <si>
     <t>Acrylglas - Tuerfenster oben</t>
   </si>
   <si>
@@ -213,12 +186,6 @@
     <t>1 Stk</t>
   </si>
   <si>
-    <t>Klappenplatte 200x200mm; 0.75mm</t>
-  </si>
-  <si>
-    <t>‎SPL1203000750200200</t>
-  </si>
-  <si>
     <t>Feder / Rückstellmechanismus 80mm</t>
   </si>
   <si>
@@ -240,9 +207,6 @@
     <t>Norelem </t>
   </si>
   <si>
-    <t>~76,61</t>
-  </si>
-  <si>
     <t>Gesamtsumme</t>
   </si>
   <si>
@@ -258,9 +222,6 @@
     <t>Summe</t>
   </si>
   <si>
-    <t>~205,34</t>
-  </si>
-  <si>
     <t xml:space="preserve">	C10000-AC03</t>
   </si>
   <si>
@@ -271,6 +232,30 @@
   </si>
   <si>
     <t>C10000-AC03</t>
+  </si>
+  <si>
+    <t>Grosschädl Stahl GmbH</t>
+  </si>
+  <si>
+    <t>Klappenplatte 200x200mm; 0.55mm</t>
+  </si>
+  <si>
+    <t>Zusatzteile</t>
+  </si>
+  <si>
+    <t>~52,67</t>
+  </si>
+  <si>
+    <t>~103,05</t>
+  </si>
+  <si>
+    <t>T bracket</t>
+  </si>
+  <si>
+    <t>~26,94</t>
+  </si>
+  <si>
+    <t>~278,78</t>
   </si>
 </sst>
 </file>
@@ -334,16 +319,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
-      <name val="Amazon Ember"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
       <name val="Times New Roman"/>
       <charset val="1"/>
     </font>
@@ -385,6 +360,18 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -424,7 +411,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -434,7 +421,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -454,9 +441,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -473,58 +457,77 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -875,12 +878,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1040,25 +1043,25 @@
       <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>7.25</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1"/>
-      <c r="B8" s="16"/>
+      <c r="B8" s="15"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" t="s">
@@ -1093,16 +1096,16 @@
     <col min="2" max="2" width="44.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1137,28 +1140,28 @@
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>29</v>
+      <c r="C3" s="34">
+        <v>223323200</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>4.2</v>
+        <v>17.91</v>
       </c>
       <c r="F3" s="4">
-        <v>4.2</v>
+        <v>17.91</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="13" t="s">
+      <c r="H3" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1166,11 +1169,11 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>70</v>
+      <c r="B4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>62</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1182,10 +1185,10 @@
         <v>13.18</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1195,11 +1198,11 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>33</v>
+      <c r="B5" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1211,10 +1214,10 @@
         <v>13.18</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1224,11 +1227,11 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>35</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1243,9 +1246,9 @@
         <v>21</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1253,11 +1256,11 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="11" t="s">
         <v>35</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1272,9 +1275,9 @@
         <v>21</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1282,18 +1285,18 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:9">
       <c r="D9" s="1"/>
@@ -1303,7 +1306,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1312,11 +1315,11 @@
     <mergeCell ref="C8:I8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{00FB3798-AAAC-4DC7-8307-15FAEE842656}"/>
-    <hyperlink ref="I7" r:id="rId2" xr:uid="{9E157C07-BD39-4FCC-9356-8F9F3DC711ED}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{2101D6C9-B54B-4F27-8533-4B3D329F16F9}"/>
-    <hyperlink ref="I5" r:id="rId4" xr:uid="{BB0B231D-4D56-4662-B1FD-83CB6B6C679E}"/>
-    <hyperlink ref="I4" r:id="rId5" xr:uid="{850B9D35-B619-4CE0-82FC-AD5809892D27}"/>
+    <hyperlink ref="I7" r:id="rId1" xr:uid="{9E157C07-BD39-4FCC-9356-8F9F3DC711ED}"/>
+    <hyperlink ref="I6" r:id="rId2" xr:uid="{2101D6C9-B54B-4F27-8533-4B3D329F16F9}"/>
+    <hyperlink ref="I5" r:id="rId3" xr:uid="{BB0B231D-4D56-4662-B1FD-83CB6B6C679E}"/>
+    <hyperlink ref="I4" r:id="rId4" xr:uid="{850B9D35-B619-4CE0-82FC-AD5809892D27}"/>
+    <hyperlink ref="I3" r:id="rId5" xr:uid="{1AD2949F-DA94-48B9-A2B9-9E513E58DAFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -1334,17 +1337,17 @@
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="A1" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
@@ -1360,10 +1363,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -1379,8 +1382,8 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>43</v>
+      <c r="B3" s="21" t="s">
+        <v>41</v>
       </c>
       <c r="C3" s="1">
         <v>103420</v>
@@ -1404,30 +1407,30 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="C4" s="34">
+        <v>223323200</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
+      <c r="E4" s="4">
+        <v>17.91</v>
+      </c>
+      <c r="F4" s="4">
+        <v>17.91</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>30</v>
+      <c r="H4" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1438,10 +1441,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>71</v>
+        <v>43</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>63</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1453,10 +1456,10 @@
         <v>4.51</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1467,18 +1470,18 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="8">
+        <v>44</v>
+      </c>
+      <c r="C6" s="7">
         <v>100922</v>
       </c>
       <c r="D6" s="1">
         <v>8</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>21.65</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1496,17 +1499,17 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
+        <v>45</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1">
@@ -1515,16 +1518,16 @@
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>100315</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>7.25</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1533,7 +1536,7 @@
       <c r="H8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="19" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1542,27 +1545,27 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>53</v>
+        <v>65</v>
+      </c>
+      <c r="C9" s="33">
+        <v>223323200</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="9">
-        <v>4</v>
-      </c>
-      <c r="F9" s="9">
-        <v>4</v>
+        <v>47</v>
+      </c>
+      <c r="E9" s="8">
+        <v>17.91</v>
+      </c>
+      <c r="F9" s="8">
+        <v>17.91</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="20" t="s">
+      <c r="H9" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="31" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1571,31 +1574,31 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>55</v>
+        <v>48</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>49</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="24">
         <v>1.67</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="24">
         <v>1.67</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" s="24" t="s">
+      <c r="H10" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="22" t="s">
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1603,40 +1606,40 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>2.9</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>2.9</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="8"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="3"/>
@@ -1646,7 +1649,7 @@
         <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1656,31 +1659,118 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{FF6F2A9B-68BA-494C-AD12-7CD830E49792}"/>
-    <hyperlink ref="I4" r:id="rId2" xr:uid="{2EFE47DB-0410-4C39-84EB-A97A40E506E0}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{215D0A79-FDBD-47E9-BA1B-6B2F2F6ACCD3}"/>
-    <hyperlink ref="I8" r:id="rId4" display="LInk" xr:uid="{50DBD59B-4175-410D-ACF6-19DBEF4FECB1}"/>
-    <hyperlink ref="I9" r:id="rId5" xr:uid="{8678A1F0-223F-4991-805D-6EC7AB143164}"/>
-    <hyperlink ref="I11" r:id="rId6" xr:uid="{FF43AA8E-0341-404D-9D7B-B37A9D083016}"/>
-    <hyperlink ref="I10" r:id="rId7" xr:uid="{2414133F-9525-449E-B258-522CBFEC1B2A}"/>
-    <hyperlink ref="I5" r:id="rId8" xr:uid="{E0A08999-7D4E-4053-9DC2-7DA08D8935D7}"/>
+    <hyperlink ref="I6" r:id="rId2" xr:uid="{215D0A79-FDBD-47E9-BA1B-6B2F2F6ACCD3}"/>
+    <hyperlink ref="I8" r:id="rId3" display="LInk" xr:uid="{50DBD59B-4175-410D-ACF6-19DBEF4FECB1}"/>
+    <hyperlink ref="I11" r:id="rId4" xr:uid="{FF43AA8E-0341-404D-9D7B-B37A9D083016}"/>
+    <hyperlink ref="I10" r:id="rId5" xr:uid="{2414133F-9525-449E-B258-522CBFEC1B2A}"/>
+    <hyperlink ref="I5" r:id="rId6" xr:uid="{E0A08999-7D4E-4053-9DC2-7DA08D8935D7}"/>
+    <hyperlink ref="I4" r:id="rId7" xr:uid="{D0AEAB0B-6997-4E48-A0EB-B96156A935E1}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{A5E0B8F1-D1CC-4E71-85D8-446B244730F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8102E2A0-AA67-44CE-8E8B-5B8829786885}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="38">
+        <v>103004</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="39">
+        <v>8.98</v>
+      </c>
+      <c r="F3" s="1">
+        <v>26.94</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{767EEAF8-8057-46D1-A4C2-96DC777FC6F9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1DD3EAF-D9B0-4B7B-8181-6B2A4E0113C7}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="27" t="s">
-        <v>62</v>
+      <c r="A1" s="25" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>96.12</v>
@@ -1688,29 +1778,40 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E3">
-        <v>32.86</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28">
-        <v>76.61</v>
+      <c r="A4" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35">
+        <v>103.05</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="A5" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="29" t="s">
-        <v>67</v>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36">
+        <v>26.94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
+++ b/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adisa.bylygbashi\Documents\SPL_3BHWII\CandyMachine_Watermelon\Stuecklisten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bulme_git\CandyMachine_Watermelon\Stuecklisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E5A73D-E833-4122-AD06-0EF846BD5941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3947CF98-4D76-4715-A7A6-43C1906BBEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
   </bookViews>
   <sheets>
     <sheet name="RahmenkonstruktionOhneTuer" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="76">
   <si>
     <t>Stückliste Rahmen ohne Tür</t>
   </si>
@@ -102,9 +102,6 @@
     <t xml:space="preserve">M3 Schrauben (Set) </t>
   </si>
   <si>
-    <t xml:space="preserve">7,98/100Stk </t>
-  </si>
-  <si>
     <t>Stahl</t>
   </si>
   <si>
@@ -249,13 +246,28 @@
     <t>~103,05</t>
   </si>
   <si>
-    <t>T bracket</t>
-  </si>
-  <si>
     <t>~26,94</t>
   </si>
   <si>
     <t>~278,78</t>
+  </si>
+  <si>
+    <t>T-slot nuts</t>
+  </si>
+  <si>
+    <t>T-brackets</t>
+  </si>
+  <si>
+    <t>17,50/50Stk</t>
+  </si>
+  <si>
+    <t>8,98/12Stk</t>
+  </si>
+  <si>
+    <t>Artikelnummer/Identifizierung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,98/100Stk </t>
   </si>
 </sst>
 </file>
@@ -500,15 +512,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -521,14 +524,25 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -878,12 +892,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1009,19 +1023,19 @@
         <v>19</v>
       </c>
       <c r="C6" s="1">
-        <v>106085</v>
-      </c>
-      <c r="D6" s="1">
-        <v>35</v>
+        <v>100933</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="E6" s="1">
-        <v>7.98</v>
+        <v>5.98</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>12</v>
@@ -1035,22 +1049,22 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1">
         <v>100315</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="17">
         <v>7.25</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>12</v>
@@ -1065,11 +1079,11 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1080,8 +1094,8 @@
     <hyperlink ref="I3" r:id="rId1" xr:uid="{91761FF5-2736-47ED-BDCD-BDB8F1DDF2F8}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{3F727FC8-A6BB-4E1E-A581-741A39FFCF2E}"/>
     <hyperlink ref="I5" r:id="rId3" xr:uid="{7B0D1198-67E3-4E8D-AFDD-540195306BD5}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{22BAB314-EFF9-4BED-9107-99201A891AB1}"/>
-    <hyperlink ref="I7" r:id="rId5" xr:uid="{C67B6DF7-A22F-456C-9DBF-7F3309EFC865}"/>
+    <hyperlink ref="I7" r:id="rId4" xr:uid="{C67B6DF7-A22F-456C-9DBF-7F3309EFC865}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{AAA935F0-739C-4E84-94AE-9AACA82B8AF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1100,12 +1114,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="A1" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1115,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -1141,9 +1155,9 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="34">
+        <v>27</v>
+      </c>
+      <c r="C3" s="31">
         <v>223323200</v>
       </c>
       <c r="D3" s="4">
@@ -1156,10 +1170,10 @@
         <v>17.91</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>64</v>
+        <v>20</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>9</v>
@@ -1170,10 +1184,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1185,10 +1199,10 @@
         <v>13.18</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1199,10 +1213,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1214,10 +1228,10 @@
         <v>13.18</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1228,10 +1242,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>34</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1243,10 +1257,10 @@
         <v>4.2</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>9</v>
@@ -1257,10 +1271,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1272,10 +1286,10 @@
         <v>4.2</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>9</v>
@@ -1286,27 +1300,27 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="1:9">
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:9">
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1333,7 +1347,7 @@
   <cols>
     <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -1342,12 +1356,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
+      <c r="A1" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
@@ -1357,16 +1371,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -1383,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1">
         <v>103420</v>
@@ -1412,9 +1426,9 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="34">
+        <v>41</v>
+      </c>
+      <c r="C4" s="31">
         <v>223323200</v>
       </c>
       <c r="D4" s="4">
@@ -1427,10 +1441,10 @@
         <v>17.91</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>64</v>
+        <v>20</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>63</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1441,10 +1455,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1456,10 +1470,10 @@
         <v>4.51</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1470,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="7">
         <v>100922</v>
@@ -1499,39 +1513,39 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="7">
         <v>100315</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="8">
         <v>7.25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>12</v>
@@ -1545,13 +1559,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="33">
+        <v>64</v>
+      </c>
+      <c r="C9" s="30">
         <v>223323200</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="8">
         <v>17.91</v>
@@ -1560,12 +1574,12 @@
         <v>17.91</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="28" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1574,10 +1588,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>49</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1589,16 +1603,16 @@
         <v>1.67</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
         <v>50</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1606,10 +1620,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1621,16 +1635,16 @@
         <v>2.9</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1646,10 +1660,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1673,15 +1687,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8102E2A0-AA67-44CE-8E8B-5B8829786885}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1717,23 +1732,23 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="38">
+      <c r="B3" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="34">
         <v>103004</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" s="39">
-        <v>8.98</v>
+      <c r="E3" s="35" t="s">
+        <v>73</v>
       </c>
       <c r="F3" s="1">
         <v>26.94</v>
       </c>
-      <c r="G3" t="s">
-        <v>21</v>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="H3" t="s">
         <v>12</v>
@@ -1742,17 +1757,57 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="39">
+        <v>2</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="34">
+        <v>103295</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="5" spans="1:9">
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>70</v>
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="34"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="1"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{767EEAF8-8057-46D1-A4C2-96DC777FC6F9}"/>
+    <hyperlink ref="I4" r:id="rId2" xr:uid="{F16339C7-A40C-4353-BF5B-0A1E99B6B2DC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1765,12 +1820,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>96.12</v>
@@ -1778,40 +1833,37 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>52.67</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4">
         <v>103.05</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36">
+      <c r="A5" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32">
         <v>26.94</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
+++ b/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bulme_git\CandyMachine_Watermelon\Stuecklisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3947CF98-4D76-4715-A7A6-43C1906BBEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BF9E1D-C407-4FAD-A102-FE4BE20CC553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
   </bookViews>
   <sheets>
     <sheet name="RahmenkonstruktionOhneTuer" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="81">
   <si>
     <t>Stückliste Rahmen ohne Tür</t>
   </si>
@@ -144,9 +144,6 @@
     <t>SPL1203000750400600</t>
   </si>
   <si>
-    <t>Rückwand mit Ausschnitt 600x400</t>
-  </si>
-  <si>
     <t>Schrauben für Bleche (zum montieren)</t>
   </si>
   <si>
@@ -268,6 +265,24 @@
   </si>
   <si>
     <t xml:space="preserve">5,98/100Stk </t>
+  </si>
+  <si>
+    <t>M3 6mm Schrauben</t>
+  </si>
+  <si>
+    <t>5,98/100</t>
+  </si>
+  <si>
+    <t>Winkel - Eckverbindung</t>
+  </si>
+  <si>
+    <t>Linsenkopfchrauben</t>
+  </si>
+  <si>
+    <t>Rückwand mit Ausschnitt 400x400</t>
+  </si>
+  <si>
+    <t>Mutter</t>
   </si>
 </sst>
 </file>
@@ -385,7 +400,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,6 +410,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -433,7 +454,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -532,6 +553,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -541,9 +565,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -892,12 +923,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1015,34 +1046,32 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1">
+    <row r="6" spans="1:9" s="43" customFormat="1">
+      <c r="A6" s="41">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="41">
         <v>100933</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="41">
         <v>5.98</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1">
@@ -1095,7 +1124,6 @@
     <hyperlink ref="I4" r:id="rId2" xr:uid="{3F727FC8-A6BB-4E1E-A581-741A39FFCF2E}"/>
     <hyperlink ref="I5" r:id="rId3" xr:uid="{7B0D1198-67E3-4E8D-AFDD-540195306BD5}"/>
     <hyperlink ref="I7" r:id="rId4" xr:uid="{C67B6DF7-A22F-456C-9DBF-7F3309EFC865}"/>
-    <hyperlink ref="I6" r:id="rId5" xr:uid="{AAA935F0-739C-4E84-94AE-9AACA82B8AF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1114,12 +1142,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1129,7 +1157,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -1172,8 +1200,8 @@
       <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="29" t="s">
-        <v>63</v>
+      <c r="H3" s="40" t="s">
+        <v>62</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>9</v>
@@ -1187,7 +1215,7 @@
         <v>29</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1202,7 +1230,7 @@
         <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1216,7 +1244,7 @@
         <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1231,7 +1259,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1271,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>33</v>
@@ -1280,10 +1308,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
@@ -1300,17 +1328,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9">
       <c r="D9" s="1"/>
@@ -1320,7 +1348,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1356,12 +1384,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="A1" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
@@ -1371,16 +1399,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -1397,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="1">
         <v>103420</v>
@@ -1426,7 +1454,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="31">
         <v>223323200</v>
@@ -1444,7 +1472,7 @@
         <v>20</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1455,10 +1483,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1473,7 +1501,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1484,7 +1512,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="7">
         <v>100922</v>
@@ -1513,17 +1541,17 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1">
@@ -1536,7 +1564,7 @@
         <v>100315</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>23</v>
@@ -1559,13 +1587,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="30">
         <v>223323200</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="8">
         <v>17.91</v>
@@ -1577,7 +1605,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I9" s="28" t="s">
         <v>9</v>
@@ -1588,10 +1616,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>48</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1606,13 +1634,13 @@
         <v>20</v>
       </c>
       <c r="H10" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
         <v>49</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1620,10 +1648,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1638,13 +1666,13 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1663,7 +1691,7 @@
         <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1687,16 +1715,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8102E2A0-AA67-44CE-8E8B-5B8829786885}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1733,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="34">
         <v>103004</v>
@@ -1742,7 +1771,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F3" s="1">
         <v>26.94</v>
@@ -1758,11 +1787,11 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="39">
+      <c r="A4" s="36">
         <v>2</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="34">
         <v>103295</v>
@@ -1771,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1">
         <v>17.5</v>
@@ -1787,27 +1816,86 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5">
+      <c r="A5" s="36">
         <v>3</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="34"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="1"/>
-      <c r="I5" s="3"/>
+      <c r="B5" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="34">
+        <v>100933</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5.98</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="36">
+        <v>4</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="B7" t="s">
+      <c r="A7" s="36">
+        <v>5</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="36">
+        <v>6</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="F7" t="s">
-        <v>68</v>
+      <c r="F10" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{767EEAF8-8057-46D1-A4C2-96DC777FC6F9}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{F16339C7-A40C-4353-BF5B-0A1E99B6B2DC}"/>
+    <hyperlink ref="I5" r:id="rId3" xr:uid="{FBAEB875-81BC-4940-9CD8-5DADD3EC1400}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1820,12 +1908,12 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2">
         <v>96.12</v>
@@ -1833,7 +1921,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3">
         <v>52.67</v>
@@ -1841,7 +1929,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>103.05</v>
@@ -1849,7 +1937,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="32"/>
       <c r="C5" s="32"/>
@@ -1860,10 +1948,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
+++ b/Stuecklisten/Stuecklisten_RahmenMitTuer_RahmenOhneTuer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bulme_git\CandyMachine_Watermelon\Stuecklisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BF9E1D-C407-4FAD-A102-FE4BE20CC553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B302F3-A4E7-4E7F-96F6-BA46B2D26981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{88596E44-11E1-465B-99E0-15FA43A2DF17}"/>
   </bookViews>
   <sheets>
     <sheet name="RahmenkonstruktionOhneTuer" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="84">
   <si>
     <t>Stückliste Rahmen ohne Tür</t>
   </si>
@@ -117,9 +117,6 @@
     <t>Zwischensumme</t>
   </si>
   <si>
-    <t>~96,12</t>
-  </si>
-  <si>
     <t>Verkleidung (ohne Tür)</t>
   </si>
   <si>
@@ -237,18 +234,9 @@
     <t>Zusatzteile</t>
   </si>
   <si>
-    <t>~52,67</t>
-  </si>
-  <si>
     <t>~103,05</t>
   </si>
   <si>
-    <t>~26,94</t>
-  </si>
-  <si>
-    <t>~278,78</t>
-  </si>
-  <si>
     <t>T-slot nuts</t>
   </si>
   <si>
@@ -264,9 +252,6 @@
     <t>Artikelnummer/Identifizierung</t>
   </si>
   <si>
-    <t xml:space="preserve">5,98/100Stk </t>
-  </si>
-  <si>
     <t>M3 6mm Schrauben</t>
   </si>
   <si>
@@ -283,13 +268,37 @@
   </si>
   <si>
     <t>Mutter</t>
+  </si>
+  <si>
+    <t>1 Set, 10Stk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,30/10Stk </t>
+  </si>
+  <si>
+    <t>cs-electronics</t>
+  </si>
+  <si>
+    <t>~90,44</t>
+  </si>
+  <si>
+    <t>~52,47</t>
+  </si>
+  <si>
+    <t>vorhanden</t>
+  </si>
+  <si>
+    <t>~50,42</t>
+  </si>
+  <si>
+    <t>~296,38</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,8 +408,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -410,12 +425,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -454,7 +463,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -556,6 +565,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -565,16 +577,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="12" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -916,19 +928,19 @@
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
     <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="16384" max="16384" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -938,7 +950,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -1046,32 +1058,34 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="43" customFormat="1">
+    <row r="6" spans="1:9" s="42" customFormat="1">
       <c r="A6" s="41">
         <v>4</v>
       </c>
       <c r="B6" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="41">
-        <v>100933</v>
+      <c r="C6" s="43">
+        <v>5051294116521</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="41">
-        <v>5.98</v>
+        <v>76</v>
+      </c>
+      <c r="E6" s="44">
+        <v>2.2999999999999998</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G6" s="41" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="42"/>
+        <v>78</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1">
@@ -1112,7 +1126,7 @@
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1124,8 +1138,10 @@
     <hyperlink ref="I4" r:id="rId2" xr:uid="{3F727FC8-A6BB-4E1E-A581-741A39FFCF2E}"/>
     <hyperlink ref="I5" r:id="rId3" xr:uid="{7B0D1198-67E3-4E8D-AFDD-540195306BD5}"/>
     <hyperlink ref="I7" r:id="rId4" xr:uid="{C67B6DF7-A22F-456C-9DBF-7F3309EFC865}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{39C95E33-048B-47C7-AF4A-2FEBA520A49F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -1142,12 +1158,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="A1" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
@@ -1157,7 +1173,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -1183,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="31">
         <v>223323200</v>
@@ -1200,8 +1216,8 @@
       <c r="G3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="40" t="s">
-        <v>62</v>
+      <c r="H3" s="37" t="s">
+        <v>61</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>9</v>
@@ -1212,10 +1228,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1227,10 +1243,10 @@
         <v>13.18</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1241,10 +1257,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1256,10 +1272,10 @@
         <v>13.18</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1270,10 +1286,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>32</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>33</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1288,7 +1304,7 @@
         <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>9</v>
@@ -1299,10 +1315,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1317,7 +1333,7 @@
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>9</v>
@@ -1328,17 +1344,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
     </row>
     <row r="9" spans="1:9">
       <c r="D9" s="1"/>
@@ -1348,7 +1364,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1384,12 +1400,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="A1" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
@@ -1399,16 +1415,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -1425,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1">
         <v>103420</v>
@@ -1454,7 +1470,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="31">
         <v>223323200</v>
@@ -1472,7 +1488,7 @@
         <v>20</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>9</v>
@@ -1483,10 +1499,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1498,10 +1514,10 @@
         <v>4.51</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>9</v>
@@ -1512,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="7">
         <v>100922</v>
@@ -1541,17 +1557,17 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1">
@@ -1564,7 +1580,7 @@
         <v>100315</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>23</v>
@@ -1587,13 +1603,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="30">
         <v>223323200</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E9" s="8">
         <v>17.91</v>
@@ -1605,7 +1621,7 @@
         <v>20</v>
       </c>
       <c r="H9" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I9" s="28" t="s">
         <v>9</v>
@@ -1616,10 +1632,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>47</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1634,13 +1650,13 @@
         <v>20</v>
       </c>
       <c r="H10" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
         <v>48</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1648,10 +1664,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1666,13 +1682,13 @@
         <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1691,7 +1707,7 @@
         <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1720,12 +1736,13 @@
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1762,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C3" s="34">
         <v>103004</v>
@@ -1771,7 +1788,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F3" s="1">
         <v>26.94</v>
@@ -1791,7 +1808,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C4" s="34">
         <v>103295</v>
@@ -1800,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F4" s="1">
         <v>17.5</v>
@@ -1820,7 +1837,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C5" s="34">
         <v>100933</v>
@@ -1829,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F5" s="1">
         <v>5.98</v>
@@ -1849,9 +1866,11 @@
         <v>4</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="34"/>
+        <v>73</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>81</v>
+      </c>
       <c r="E6" s="35"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -1862,9 +1881,11 @@
         <v>5</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="34"/>
+        <v>72</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>81</v>
+      </c>
       <c r="E7" s="35"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1875,9 +1896,11 @@
         <v>6</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>81</v>
+      </c>
       <c r="E8" s="35"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1888,7 +1911,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1908,28 +1931,28 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2">
-        <v>96.12</v>
+        <v>90.44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3">
-        <v>52.67</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4">
         <v>103.05</v>
@@ -1937,21 +1960,21 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" s="32"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="E5" s="32">
-        <v>26.94</v>
+        <v>50.42</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
